--- a/work_request_forms/041_maid_service_work_order--work_request_forms.xlsx
+++ b/work_request_forms/041_maid_service_work_order--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-time',_'value':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-time', 'value': 'one-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'recurring',_'value':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Recurring', 'value': 'recurring'}</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'scheduled',_'value':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Scheduled', 'value': 'scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancel',_'value':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancel', 'value': 'cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
